--- a/dist/SUBMISSION_FINAL/P3_Vietnam_JED/p3_vietnam_apjm_replication_data.xlsx
+++ b/dist/SUBMISSION_FINAL/P3_Vietnam_JED/p3_vietnam_apjm_replication_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Regression_Coefficients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Turning_Points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Figure_Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Figures_Embedded" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,25 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +191,161 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="4191000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>136</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>168</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="2381250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +771,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1360,7 +1540,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -3149,7 +3328,7 @@
         <v>0.05</v>
       </c>
       <c r="G49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0135</v>
@@ -9957,7 +10136,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -10075,29 +10253,21 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Figure 1 is a conceptual diagram (not a chart with tabular data). It depicts the relationships among the independent variable, the dependent variable, the two moderators, the control set, and the four hypotheses tested in the paper.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Hypotheses summarised in the diagram</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10159,17 +10329,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Controls (top dashed box in the diagram)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10177,19 +10343,14 @@
           <t>lnEmp (firm size); FirmAge; ForeignOwned (b2b &gt; 0); Sector FE (a4b/a4a 1-digit ISIC); Wave FE (in pooled).</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' construction.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6">
@@ -10215,19 +10376,14 @@
           <t>Sample: Vietnam 2009  (N = 989)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10235,7 +10391,6 @@
           <t>M2: lnLP = b0 + b1*FSTSc + b2*FSTSc^2 + lnEmp + FirmAge + ForeignOwned + sector FE.  OLS with HC1 robust standard errors.</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10243,19 +10398,14 @@
           <t>Controls held at within-sample means; sector and wave fixed effects at modal value.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>Coefficients</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10277,10 +10427,7 @@
         <v>-1.773817104956196</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -10291,17 +10438,13 @@
         <v>46.25</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10309,7 +10452,6 @@
           <t>Data       — FSTS grid (%), predicted lnLP, 95% CI lower/upper</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10317,7 +10459,6 @@
           <t>Chart      — native Excel line chart of the predicted curve</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10325,19 +10466,14 @@
           <t>Image      — rendered PNG (sanity check)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' calculations.</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6">
@@ -10363,19 +10499,14 @@
           <t>Sample: Vietnam 2015  (N = 956)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10383,7 +10514,6 @@
           <t>M2: lnLP = b0 + b1*FSTSc + b2*FSTSc^2 + lnEmp + FirmAge + ForeignOwned + sector FE.  OLS with HC1 robust standard errors.</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10391,19 +10521,14 @@
           <t>Controls held at within-sample means; sector and wave fixed effects at modal value.</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>Coefficients</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10425,10 +10550,7 @@
         <v>-2.11500510919916</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
@@ -10439,17 +10561,13 @@
         <v>39.32</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10457,7 +10575,6 @@
           <t>Data       — FSTS grid (%), predicted lnLP, 95% CI lower/upper</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10465,7 +10582,6 @@
           <t>Chart      — native Excel line chart of the predicted curve</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10473,19 +10589,14 @@
           <t>Image      — rendered PNG (sanity check)</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' calculations.</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6">
@@ -10511,19 +10622,14 @@
           <t>Sample: Vietnam 2023  (N = 1,013)</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10531,7 +10637,6 @@
           <t>M2: lnLP = b0 + b1*FSTSc + b2*FSTSc^2 + lnEmp + FirmAge + ForeignOwned + sector FE.  OLS with HC1 robust standard errors.</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10539,19 +10644,14 @@
           <t>Controls held at within-sample means; sector and wave fixed effects at modal value.</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>Coefficients</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10573,10 +10673,7 @@
         <v>-1.686217912245887</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
-    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -10587,17 +10684,13 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10605,7 +10698,6 @@
           <t>Data       — FSTS grid (%), predicted lnLP, 95% CI lower/upper</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10613,7 +10705,6 @@
           <t>Chart      — native Excel line chart of the predicted curve</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10621,19 +10712,14 @@
           <t>Image      — rendered PNG (sanity check)</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' calculations.</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6">
@@ -10659,19 +10745,14 @@
           <t>Sample: Pooled Vietnam (2009/2015/2023)  (N = 2,958)</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10679,7 +10760,6 @@
           <t>M2: lnLP = b0 + b1*FSTSc + b2*FSTSc^2 + lnEmp + FirmAge + ForeignOwned + sector FE + wave FE.  OLS with HC1 robust standard errors.</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10687,19 +10767,14 @@
           <t>Controls held at within-sample means; sector and wave fixed effects at modal value.</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
           <t>Coefficients</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10721,10 +10796,7 @@
         <v>-1.909054793116382</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-    </row>
+    <row r="98"/>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
@@ -10735,17 +10807,13 @@
         <v>39.72</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
-    </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10753,7 +10821,6 @@
           <t>Data       — FSTS grid (%), predicted lnLP, 95% CI lower/upper</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10761,7 +10828,6 @@
           <t>Chart      — native Excel line chart of the predicted curve</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10769,19 +10835,14 @@
           <t>Image      — rendered PNG (sanity check)</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' calculations.</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6">
@@ -10807,19 +10868,14 @@
           <t>Sample: pooled Vietnam 2009/2015/2023 (N = 2,958)</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
           <t>Specification</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10827,7 +10883,6 @@
           <t>Pooled M8: lnLP = b0 + b1*FSTSc + b2*FSTSc^2 + b3*TCI_z + b4*DAI_z + b5*FSTSc*DAI_z + b6*FSTSc^2*DAI_z + lnEmp + FirmAge + ForeignOwned + sector FE + wave FE.  OLS with HC1 robust standard errors.</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10835,19 +10890,14 @@
           <t>Controls held at sample means; sector and wave fixed effects at modal value. Moderator quantiles taken from the pooled sample.</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="116"/>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
           <t>DAI_z quantiles</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10869,17 +10919,13 @@
         <v>1.033511292731806</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr"/>
-    </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>TCI_z quantiles</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10901,17 +10947,13 @@
         <v>-0.4806479368867119</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr"/>
-    </row>
+    <row r="124"/>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10919,7 +10961,6 @@
           <t>Data 3a    — FSTS grid, predicted lnLP at low / high DAI_z (TCI_z held at mean)</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10927,7 +10968,6 @@
           <t>Chart 3a   — native Excel line chart of Panel 3a</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10935,7 +10975,6 @@
           <t>Data 3b    — FSTS grid, predicted lnLP at low / high TCI_z (DAI_z held at mean)</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10943,7 +10982,6 @@
           <t>Chart 3b   — native Excel line chart of Panel 3b</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10951,21 +10989,155 @@
           <t>Image      — rendered PNG of Figure 3 (sanity check)</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
           <t>Source: World Bank Enterprise Surveys (https://www.enterprisesurveys.org); authors' calculations on Vietnam 2009/2015/2023 pooled.</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>P3_Vietnam_JED — Embedded Figures (data-driven, source-traceable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Each figure below was rendered from a CSV / data file produced by the paper's Stata or R replication pipeline. Provenance is listed under each figure. See 'STATA_REPLICATION_GUIDE.md' (Vietnamese + English) for end-to-end reproduction instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Figure 1: figure_1_conceptual_model.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: scripts/render_conceptual_models.py → matplotlib (theoretical diagram, not data-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2: figure_2a.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p3/replication/figures/ ← p3/replication/coefs_main_models.csv (Stata 02_run_models.do)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Figure 3: figure_2b.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p3/replication/figures/ ← p3/replication/coefs_main_models.csv (Stata 02_run_models.do)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Figure 4: figure_2c.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p3/replication/figures/ ← p3/replication/coefs_main_models.csv (Stata 02_run_models.do)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>Figure 5: figure_2d.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p3/replication/figures/ ← p3/replication/coefs_main_models.csv (Stata 02_run_models.do)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>Figure 6: figure_3_moderator_marginals.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p3/replication/figures/ ← p3/replication/moderator_marginal_effects.csv (Stata margins post-estimation)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A136:H136"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A167:H167"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A40:H40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>